--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -389,7 +389,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -594,7 +594,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -623,7 +623,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -703,7 +703,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -993,7 +993,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1154,7 +1154,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1276,7 +1276,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1547,7 +1547,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1579,7 +1579,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1701,7 +1701,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1713,7 +1713,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1741,7 +1741,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1821,7 +1821,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1871,7 +1871,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1904,7 +1904,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1941,7 +1941,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1963,7 +1963,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -4495,7 +4495,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>200</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>223</v>
       </c>
@@ -5097,7 +5097,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>238</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>252</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>270</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>306</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>356</v>
       </c>
@@ -9081,7 +9081,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>383</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>432</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>439</v>
       </c>
@@ -10411,7 +10411,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>460</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>468</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>477</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>486</v>
       </c>
@@ -14381,7 +14381,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>629</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>639</v>
       </c>
@@ -14985,7 +14985,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
         <v>645</v>
       </c>
@@ -15107,7 +15107,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>654</v>
       </c>
@@ -15475,12 +15475,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP108">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-bodytemp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
